--- a/Operacional/Modelos/CRONOGRAMA_COORDENADOR.xlsx
+++ b/Operacional/Modelos/CRONOGRAMA_COORDENADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="EstaPasta_de_trabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CIPOLATTI\SISTEMAS\Operacional\Operacional\Modelos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Codex\2026-05-21\clona-o-repositorio-wognascimento-financeiro-git\Operacional\Operacional\Modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9AB311-E87E-4B41-905C-4A3855A0FE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0482A7A-85EC-4B98-8513-54C52C184B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="11805" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COORDENADOR" sheetId="1" r:id="rId1"/>
@@ -335,22 +335,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -804,19 +804,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="13"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
       <c r="V1" s="6" t="s">
         <v>20</v>
       </c>
@@ -825,58 +825,58 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
     </row>
@@ -994,10 +994,10 @@
       <c r="W7" s="9"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="16"/>
+      <c r="D8" s="18"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -1018,10 +1018,10 @@
       <c r="W8" s="9"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="16"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -1042,10 +1042,10 @@
       <c r="W9" s="9"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="16"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -1066,10 +1066,10 @@
       <c r="W10" s="9"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="16"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="5">
         <f>SUM(E8:E10)</f>
         <v>0</v>
@@ -1336,7 +1336,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
